--- a/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,290 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.15</v>
+        <v>5.5</v>
       </c>
       <c r="C2" t="n">
         <v>3.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="C3" t="n">
         <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="C4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" t="n">
         <v>5.75</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
-      </c>
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,27 +576,39 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>t4ZkclrT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>f9bfyqFM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -606,7 +618,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>bHLf4sq9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -616,7 +628,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -626,7 +638,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -636,7 +648,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -646,7 +658,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -656,7 +668,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -666,7 +678,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -676,7 +688,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -686,7 +698,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -696,7 +708,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -706,7 +718,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -716,7 +728,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -726,12 +738,192 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.78</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
@@ -548,13 +548,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="C8" t="n">
         <v>3.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="9">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="C31" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="D31" t="n">
-        <v>4.47</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="32">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="C33" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="D33" t="n">
         <v>2.48</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="C35" t="n">
         <v>3.25</v>
       </c>
       <c r="D35" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="36">

--- a/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="C3" t="n">
         <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="C5" t="n">
         <v>3.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="C28" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="D28" t="n">
         <v>2.55</v>
@@ -788,13 +788,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="C29" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="D29" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="30">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="C30" t="n">
         <v>3.2</v>
       </c>
       <c r="D30" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="31">
@@ -820,13 +820,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="C31" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="D31" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="32">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="C32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="D32" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="33">
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="C33" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="D33" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="34">
@@ -868,13 +868,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="C34" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="D34" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="35">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="C35" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="D35" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="36">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="C36" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="D36" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="37">
@@ -916,13 +916,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="C37" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="D37" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/italy/data_preparation/format_data/df_match_odds_form.xlsx
@@ -452,13 +452,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="C2" t="n">
         <v>3.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="3">
@@ -611,9 +611,15 @@
           <t>f9bfyqFM</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -621,29 +627,47 @@
           <t>bHLf4sq9</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.73</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>6.17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.23</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
